--- a/data/03_gold/controle_viaturas_final.xlsx
+++ b/data/03_gold/controle_viaturas_final.xlsx
@@ -484,16 +484,8 @@
           <t>10/05/2026 15:49:00</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>RUA DONA NENE, Nº 117 - CENTRO - CAPETINGA</t>
@@ -671,7 +663,11 @@
           <t>RODOVIA MG 050, Km 332 - PASSOS</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DANIEL ANCONI DE SOUSA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -838,16 +834,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5691</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>RUA ADONIRA MARIA DE JESUS, Nº 188 - SANTO ANTONIO - PASSOS</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EVERSON CRUZ SILVA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -870,10 +874,14 @@
           <t>10/05/2026 13:18:00</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5691</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -881,7 +889,11 @@
           <t>RUA CACHOEIRAS, Nº 190 - NOVO HORIZONTE - PASSOS</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EVERSON CRUZ SILVA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -904,14 +916,26 @@
           <t>10/05/2026 16:28:00</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5963</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>RUA FELIPE DOS SANTOS, Nº 20 - SANTA CASA - PASSOS</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>RAPHAEL DA SILVA CARDOSO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -934,14 +958,26 @@
           <t>10/05/2026 19:39:00</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5963</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>RUA JOAQUIM LOPES, Nº 231 - PENHA - PASSOS</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>WILAR ISAAC DE CARVALHO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -964,14 +1000,26 @@
           <t>10/05/2026 20:09:00</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6235</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>RUA SAO PAULO, Nº S/N - SAO BENEDITO - PASSOS</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>VINICIUS DE SOUZA SILVEIRA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
